--- a/docs/downloads/07/tbl_securisation_marovoay_tous.xlsx
+++ b/docs/downloads/07/tbl_securisation_marovoay_tous.xlsx
@@ -374,7 +374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -389,7 +389,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -404,7 +404,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -419,7 +419,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -434,7 +434,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -449,7 +449,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -464,7 +464,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
